--- a/untranslated/downloads/data-excel/5.b.1.xlsx
+++ b/untranslated/downloads/data-excel/5.b.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14175" windowHeight="8070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -548,7 +548,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -679,6 +679,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -986,13 +989,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I161"/>
+  <dimension ref="A1:J161"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="38.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>74</v>
       </c>
@@ -1006,7 +1009,7 @@
       <c r="E1" s="24"/>
       <c r="F1" s="24"/>
     </row>
-    <row r="2" spans="1:9" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>55</v>
       </c>
@@ -1020,7 +1023,7 @@
       <c r="E2" s="24"/>
       <c r="F2" s="24"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24"/>
       <c r="B3" s="15"/>
       <c r="C3" s="24"/>
@@ -1028,7 +1031,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="24"/>
     </row>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1056,8 +1059,11 @@
       <c r="I4" s="40">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="40">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
         <v>24</v>
       </c>
@@ -1085,8 +1091,11 @@
       <c r="I5" s="41">
         <v>93.173765489833443</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" s="48">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
         <v>25</v>
       </c>
@@ -1102,8 +1111,9 @@
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
       <c r="I6" s="42"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" s="49"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>94</v>
       </c>
@@ -1131,8 +1141,11 @@
       <c r="I7" s="42">
         <v>96.812712627386361</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="49">
+        <v>92.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>95</v>
       </c>
@@ -1160,8 +1173,11 @@
       <c r="I8" s="42">
         <v>90.898640492973286</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" s="49">
+        <v>89.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
         <v>73</v>
       </c>
@@ -1177,8 +1193,9 @@
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
       <c r="I9" s="42"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" s="49"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>49</v>
       </c>
@@ -1206,8 +1223,11 @@
       <c r="I10" s="42">
         <v>94.496681726238052</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="49">
+        <v>91.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>50</v>
       </c>
@@ -1235,8 +1255,11 @@
       <c r="I11" s="42">
         <v>92.051111227758497</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" s="49">
+        <v>90.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
         <v>26</v>
       </c>
@@ -1252,8 +1275,9 @@
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
       <c r="I12" s="42"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="49"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -1281,8 +1305,11 @@
       <c r="I13" s="42">
         <v>93.467281976878269</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" s="49">
+        <v>92.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>28</v>
       </c>
@@ -1310,8 +1337,11 @@
       <c r="I14" s="42">
         <v>88.48588518782671</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" s="49">
+        <v>89.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -1339,8 +1369,11 @@
       <c r="I15" s="42">
         <v>96.547004486826353</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" s="49">
+        <v>93.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>30</v>
       </c>
@@ -1368,8 +1401,11 @@
       <c r="I16" s="42">
         <v>94.583072668354262</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="49">
+        <v>93.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>31</v>
       </c>
@@ -1397,8 +1433,11 @@
       <c r="I17" s="42">
         <v>86.45869177272472</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" s="49">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>32</v>
       </c>
@@ -1426,8 +1465,11 @@
       <c r="I18" s="42">
         <v>95.993585670302522</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" s="49">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>33</v>
       </c>
@@ -1455,8 +1497,11 @@
       <c r="I19" s="42">
         <v>97.926951512122756</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="49">
+        <v>94.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>34</v>
       </c>
@@ -1484,8 +1529,11 @@
       <c r="I20" s="42">
         <v>98.078221536867233</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="49">
+        <v>92.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>35</v>
       </c>
@@ -1513,8 +1561,11 @@
       <c r="I21" s="42">
         <v>95.401412953206219</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" s="49">
+        <v>90.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="30" t="s">
         <v>105</v>
       </c>
@@ -1530,8 +1581,9 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22" s="49"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
         <v>43</v>
       </c>
@@ -1559,8 +1611,11 @@
       <c r="I23" s="42">
         <v>91.594879782501508</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="J23" s="49">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
         <v>102</v>
       </c>
@@ -1588,8 +1643,11 @@
       <c r="I24" s="42">
         <v>95.772439637078136</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J24" s="49">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
         <v>103</v>
       </c>
@@ -1617,8 +1675,11 @@
       <c r="I25" s="42">
         <v>88.002462790348886</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J25" s="49">
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
         <v>107</v>
       </c>
@@ -1635,7 +1696,7 @@
       <c r="H26" s="42"/>
       <c r="I26" s="42"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>76</v>
       </c>
@@ -1663,8 +1724,11 @@
       <c r="I27" s="42">
         <v>71.333678883516242</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J27" s="49">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
         <v>36</v>
       </c>
@@ -1692,8 +1756,11 @@
       <c r="I28" s="42">
         <v>86.907002993165165</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28" s="49">
+        <v>85.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>37</v>
       </c>
@@ -1721,8 +1788,11 @@
       <c r="I29" s="42">
         <v>92.987655042463771</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J29" s="49">
+        <v>91.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
         <v>38</v>
       </c>
@@ -1750,8 +1820,11 @@
       <c r="I30" s="42">
         <v>97.28771382890011</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J30" s="49">
+        <v>94.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>39</v>
       </c>
@@ -1779,8 +1852,11 @@
       <c r="I31" s="42">
         <v>98.722923142249741</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J31" s="49">
+        <v>94.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
         <v>93</v>
       </c>
@@ -1796,8 +1872,9 @@
       <c r="G32" s="42"/>
       <c r="H32" s="42"/>
       <c r="I32" s="42"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J32" s="49"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>82</v>
       </c>
@@ -1825,8 +1902,11 @@
       <c r="I33" s="43">
         <v>95.114617666585886</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J33" s="49">
+        <v>92.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
         <v>83</v>
       </c>
@@ -1854,8 +1934,11 @@
       <c r="I34" s="43">
         <v>93.151802320339755</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J34" s="49">
+        <v>90.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
         <v>84</v>
       </c>
@@ -1883,8 +1966,11 @@
       <c r="I35" s="43">
         <v>89.969910976392214</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J35" s="49">
+        <v>91.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
         <v>85</v>
       </c>
@@ -1912,8 +1998,11 @@
       <c r="I36" s="43">
         <v>92.498347032504768</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J36" s="49">
+        <v>89.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20" t="s">
         <v>86</v>
       </c>
@@ -1941,8 +2030,11 @@
       <c r="I37" s="44">
         <v>95.135670598922459</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J37" s="50">
+        <v>91.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="45" t="s">
         <v>57</v>
       </c>
@@ -1957,7 +2049,7 @@
       <c r="F38" s="28"/>
       <c r="G38" s="13"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1966,7 +2058,7 @@
       <c r="F39" s="4"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1975,7 +2067,7 @@
       <c r="F40" s="4"/>
       <c r="G40" s="13"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1984,7 +2076,7 @@
       <c r="F41" s="4"/>
       <c r="G41" s="14"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1992,7 +2084,7 @@
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -2000,7 +2092,7 @@
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -2008,7 +2100,7 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -2016,7 +2108,7 @@
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -2024,7 +2116,7 @@
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -2032,7 +2124,7 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
